--- a/Team-Data/2008-09/3-16-2008-09.xlsx
+++ b/Team-Data/2008-09/3-16-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -757,7 +824,7 @@
         <v>23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>11</v>
@@ -781,7 +848,7 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>0.742</v>
+        <v>0.746</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J3" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="K3" t="n">
         <v>0.485</v>
@@ -873,31 +940,31 @@
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U3" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
         <v>7.8</v>
@@ -906,22 +973,22 @@
         <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA3" t="n">
         <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -945,22 +1012,22 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>0.433</v>
+        <v>0.424</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="J4" t="n">
-        <v>76.7</v>
+        <v>76.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.454</v>
@@ -1052,34 +1119,34 @@
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O4" t="n">
         <v>17.7</v>
       </c>
       <c r="P4" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.744</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T4" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V4" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1091,31 +1158,31 @@
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF4" t="n">
         <v>18</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19</v>
       </c>
       <c r="AG4" t="n">
         <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1133,7 +1200,7 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
@@ -1151,7 +1218,7 @@
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU4" t="n">
         <v>12</v>
@@ -1160,7 +1227,7 @@
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
         <v>16</v>
@@ -1169,16 +1236,16 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
         <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.439</v>
+        <v>0.448</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,67 +1292,67 @@
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
         <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.791</v>
+        <v>0.789</v>
       </c>
       <c r="R5" t="n">
         <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
         <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1306,7 +1373,7 @@
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1327,10 +1394,10 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1339,13 +1406,13 @@
         <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="n">
         <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.803</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
         <v>0.469</v>
@@ -1416,16 +1483,16 @@
         <v>8.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="O6" t="n">
         <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0.754</v>
@@ -1434,16 +1501,16 @@
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
         <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.7</v>
@@ -1452,22 +1519,22 @@
         <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.6</v>
+        <v>100.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,10 +1549,10 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1500,7 +1567,7 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1515,25 +1582,25 @@
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1694,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -1753,61 +1820,61 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.632</v>
+        <v>0.627</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J8" t="n">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.466</v>
       </c>
       <c r="L8" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>17.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="O8" t="n">
         <v>23.1</v>
       </c>
       <c r="P8" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
         <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="U8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
         <v>8.5</v>
@@ -1819,19 +1886,19 @@
         <v>5.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>103</v>
+        <v>102.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1843,25 +1910,25 @@
         <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1873,13 +1940,13 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1900,13 +1967,13 @@
         <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2043,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2055,13 +2122,13 @@
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2264,13 +2331,13 @@
         <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2366,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.638</v>
+        <v>0.632</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J11" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.451</v>
       </c>
       <c r="L11" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M11" t="n">
         <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="O11" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.806</v>
+        <v>0.804</v>
       </c>
       <c r="R11" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S11" t="n">
         <v>32.4</v>
       </c>
       <c r="T11" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V11" t="n">
         <v>14.3</v>
@@ -2359,28 +2426,28 @@
         <v>6.9</v>
       </c>
       <c r="X11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>21</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2410,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2431,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2449,10 +2516,10 @@
         <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2629,7 @@
         <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2580,25 +2647,25 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
         <v>22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR12" t="n">
         <v>11</v>
@@ -2613,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
         <v>20</v>
@@ -2628,7 +2695,7 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2783,7 +2850,7 @@
         <v>27</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>0.803</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K14" t="n">
         <v>0.477</v>
@@ -2872,31 +2939,31 @@
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
         <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
         <v>13.5</v>
@@ -2914,25 +2981,25 @@
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.4</v>
+        <v>108.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>17</v>
@@ -2950,25 +3017,25 @@
         <v>14</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,13 +3050,13 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>0.258</v>
+        <v>0.262</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3051,19 +3118,19 @@
         <v>0.45</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>13.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
         <v>0.753</v>
@@ -3072,13 +3139,13 @@
         <v>10.5</v>
       </c>
       <c r="S15" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T15" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="U15" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="V15" t="n">
         <v>15.1</v>
@@ -3102,16 +3169,16 @@
         <v>93.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,10 +3202,10 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
@@ -3147,7 +3214,7 @@
         <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
@@ -3171,13 +3238,13 @@
         <v>27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3299,7 +3366,7 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
@@ -3323,7 +3390,7 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
@@ -3335,10 +3402,10 @@
         <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3359,7 +3426,7 @@
         <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>0.456</v>
+        <v>0.449</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,10 +3476,10 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
         <v>6.1</v>
@@ -3421,10 +3488,10 @@
         <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
         <v>25.8</v>
@@ -3436,16 +3503,16 @@
         <v>12.2</v>
       </c>
       <c r="S17" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3457,34 +3524,34 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3502,10 +3569,10 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3517,7 +3584,7 @@
         <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3544,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI18" t="n">
         <v>12</v>
@@ -3675,16 +3742,16 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>15</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
         <v>18</v>
@@ -3693,7 +3760,7 @@
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
         <v>18</v>
@@ -3723,7 +3790,7 @@
         <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -3755,19 +3822,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
         <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="H19" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I19" t="n">
         <v>35.8</v>
@@ -3779,19 +3846,19 @@
         <v>0.447</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N19" t="n">
         <v>0.38</v>
       </c>
       <c r="O19" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P19" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q19" t="n">
         <v>0.783</v>
@@ -3803,46 +3870,46 @@
         <v>29.3</v>
       </c>
       <c r="T19" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U19" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V19" t="n">
         <v>13.2</v>
       </c>
       <c r="W19" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y19" t="n">
         <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.7</v>
+        <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>10</v>
@@ -3857,25 +3924,25 @@
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
         <v>22</v>
@@ -3884,16 +3951,16 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV19" t="n">
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY19" t="n">
         <v>16</v>
@@ -3905,7 +3972,7 @@
         <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
         <v>41</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>0.621</v>
+        <v>0.631</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3958,16 +4025,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O20" t="n">
         <v>18.4</v>
@@ -3976,55 +4043,55 @@
         <v>22.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
         <v>39.9</v>
       </c>
       <c r="U20" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V20" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>96</v>
+        <v>96.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG20" t="n">
         <v>7</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>9</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4045,28 +4112,28 @@
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO20" t="n">
         <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
       </c>
       <c r="AU20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
@@ -4081,16 +4148,16 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG21" t="n">
         <v>19</v>
       </c>
-      <c r="AG21" t="n">
-        <v>20</v>
-      </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4239,7 +4306,7 @@
         <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -4301,64 +4368,64 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" t="n">
         <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>0.284</v>
+        <v>0.273</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J22" t="n">
         <v>81.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P22" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q22" t="n">
         <v>0.787</v>
       </c>
       <c r="R22" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S22" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T22" t="n">
         <v>43</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
         <v>16.7</v>
       </c>
       <c r="W22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X22" t="n">
         <v>4.4</v>
@@ -4367,19 +4434,19 @@
         <v>5</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>97.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.4</v>
+        <v>-5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,16 +4458,16 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -4412,10 +4479,10 @@
         <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4445,13 +4512,13 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -4561,25 +4628,25 @@
         <v>7.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
@@ -4615,13 +4682,13 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>24</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -4758,13 +4825,13 @@
         <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
         <v>16</v>
       </c>
       <c r="AK24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
         <v>30</v>
@@ -4809,7 +4876,7 @@
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>11</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -5032,52 +5099,52 @@
         <v>66</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>0.636</v>
+        <v>0.621</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
       </c>
       <c r="M26" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O26" t="n">
         <v>18.8</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="O26" t="n">
-        <v>18.9</v>
-      </c>
       <c r="P26" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U26" t="n">
         <v>20.2</v>
@@ -5089,43 +5156,43 @@
         <v>6.7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
         <v>8</v>
@@ -5134,19 +5201,19 @@
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,13 +5222,13 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5173,16 +5240,16 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA26" t="n">
         <v>13</v>
       </c>
-      <c r="BA26" t="n">
-        <v>12</v>
-      </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5310,7 +5377,7 @@
         <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>12</v>
@@ -5319,7 +5386,7 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5331,7 +5398,7 @@
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS27" t="n">
         <v>24</v>
@@ -5346,7 +5413,7 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28" t="n">
         <v>44</v>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.677</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
@@ -5414,37 +5481,37 @@
         <v>79.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L28" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
         <v>19.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="O28" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P28" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T28" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U28" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V28" t="n">
         <v>12.1</v>
@@ -5453,25 +5520,25 @@
         <v>5.8</v>
       </c>
       <c r="X28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5492,10 +5559,10 @@
         <v>19</v>
       </c>
       <c r="AK28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5531,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -5575,49 +5642,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" t="n">
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>0.353</v>
+        <v>0.358</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J29" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
         <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O29" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P29" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q29" t="n">
         <v>0.826</v>
       </c>
       <c r="R29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S29" t="n">
         <v>30.4</v>
@@ -5629,7 +5696,7 @@
         <v>21.8</v>
       </c>
       <c r="V29" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W29" t="n">
         <v>6.2</v>
@@ -5638,28 +5705,28 @@
         <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z29" t="n">
         <v>19.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.7</v>
+        <v>-3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
         <v>23</v>
@@ -5668,28 +5735,28 @@
         <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>24</v>
       </c>
       <c r="AM29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>25</v>
@@ -5707,7 +5774,7 @@
         <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5725,10 +5792,10 @@
         <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
@@ -5883,19 +5950,19 @@
         <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>19</v>
@@ -5904,7 +5971,7 @@
         <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6038,7 +6105,7 @@
         <v>13</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6083,7 +6150,7 @@
         <v>21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-16-2008-09</t>
+          <t>2009-03-16</t>
         </is>
       </c>
     </row>
